--- a/materials/自己PR文を書く/教員用評価シート.xlsx
+++ b/materials/自己PR文を書く/教員用評価シート.xlsx
@@ -98,17 +98,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,10 +164,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -541,21 +538,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -568,11 +569,11 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>単元目標：自分の体験（具体）とそこから得た力や成長（抽象）とのつながりを整理し、高校入試の自己評価資料という目的に応じて、伝えたいことを明確にした自己PR文を書くことができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>単元目標：自分の体験（具体）とそこから得た力や成長（抽象）とのつながりを整理して自己PR文を書くとともに、グループでの発表を聞き合う中で、聴き取った内容を具体的な観点から評価する力を身に付ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>クラス</t>
@@ -603,44 +604,70 @@
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>自己PR文
-（まとめ活動）</t>
+（作文）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>AI評価
-(S〜D)</t>
+          <t>自己PR文
+AI評価(S〜D)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>AIコメント</t>
+          <t>自己PR文
+AIコメント</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>教師最終評価
-(S〜D)</t>
+          <t>自己PR文
+教師最終評価(S〜D)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>自己評価
-(S〜D)</t>
+          <t>聞き取り評価①
+（発表者・内容）</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>評価差考察</t>
+          <t>聞き取り評価②
+（発表者・内容）</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>聞き取り評価③
+（発表者・内容）</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>聞き取り評価
+AI評価(S〜D)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>聞き取り評価
+AIコメント</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>聞き取り評価
+教師最終評価(S〜D)</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
           <t>振り返り</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>3</t>
@@ -688,21 +715,37 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
+          <t>鈴木さん：練習で声が小さかった人に個別に声をかけていたのが良かった。誰が苦手か具体的に分かって伝わった。</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>佐藤さん：委員会活動で決め方に困ったとき、多数決ではなく一人ずつ意見を聞いたと言っていて、配慮の具体例が分かりやすかった。</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>AI評価と自己評価が一致した。</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>自分の言葉で書けたことが自信になった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>話し手の言葉を引用しながら、2人分とも具体的な根拠を挙げて評価できている。</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>友達の発表を聞いて、自分にはなかった視点に気づけた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
@@ -712,11 +755,15 @@
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="8" t="n"/>
-      <c r="J5" s="9" t="n"/>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="8" t="n"/>
+      <c r="P5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
@@ -726,11 +773,15 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="8" t="n"/>
-      <c r="J6" s="9" t="n"/>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
@@ -740,11 +791,15 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="8" t="n"/>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
@@ -754,11 +809,15 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="9" t="n"/>
+      <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
@@ -768,11 +827,15 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="8" t="n"/>
-      <c r="J9" s="9" t="n"/>
+      <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="P9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
@@ -782,11 +845,15 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="9" t="n"/>
+      <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
@@ -796,11 +863,15 @@
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="8" t="n"/>
-      <c r="J11" s="9" t="n"/>
+      <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
@@ -810,11 +881,15 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="8" t="n"/>
-      <c r="J12" s="9" t="n"/>
+      <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
@@ -824,11 +899,15 @@
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="8" t="n"/>
-      <c r="J13" s="9" t="n"/>
+      <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
@@ -838,11 +917,15 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
@@ -852,11 +935,15 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="8" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="8" t="n"/>
+      <c r="P15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
@@ -866,11 +953,15 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="8" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
@@ -880,11 +971,15 @@
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="8" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
@@ -894,11 +989,15 @@
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="8" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
@@ -908,11 +1007,15 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="8" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
@@ -922,11 +1025,15 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="8" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
@@ -936,11 +1043,15 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="8" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
@@ -950,11 +1061,15 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="8" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
@@ -964,11 +1079,15 @@
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="8" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
@@ -978,11 +1097,15 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
@@ -992,11 +1115,15 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="8" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="8" t="n"/>
+      <c r="P25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
@@ -1006,11 +1133,15 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="8" t="n"/>
-      <c r="J26" s="9" t="n"/>
+      <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
@@ -1020,11 +1151,15 @@
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="8" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="8" t="n"/>
+      <c r="P27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
@@ -1034,11 +1169,15 @@
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="8" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="8" t="n"/>
+      <c r="P28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
@@ -1048,11 +1187,15 @@
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="8" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="8" t="n"/>
+      <c r="P29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
@@ -1062,11 +1205,15 @@
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="8" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="8" t="n"/>
+      <c r="P30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
@@ -1076,11 +1223,15 @@
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="8" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="8" t="n"/>
+      <c r="P31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
@@ -1090,11 +1241,15 @@
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="8" t="n"/>
-      <c r="J32" s="9" t="n"/>
+      <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="8" t="n"/>
+      <c r="P32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
@@ -1104,11 +1259,15 @@
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="8" t="n"/>
-      <c r="J33" s="9" t="n"/>
+      <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="8" t="n"/>
+      <c r="P33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
@@ -1118,11 +1277,15 @@
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="8" t="n"/>
-      <c r="J34" s="9" t="n"/>
+      <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="8" t="n"/>
+      <c r="P34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
@@ -1132,11 +1295,15 @@
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="8" t="n"/>
-      <c r="J35" s="9" t="n"/>
+      <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="6" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="8" t="n"/>
+      <c r="P35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
@@ -1146,11 +1313,15 @@
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="8" t="n"/>
-      <c r="J36" s="9" t="n"/>
+      <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="8" t="n"/>
+      <c r="P36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
@@ -1160,11 +1331,15 @@
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="8" t="n"/>
-      <c r="J37" s="9" t="n"/>
+      <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="8" t="n"/>
+      <c r="P37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
@@ -1174,11 +1349,15 @@
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="8" t="n"/>
-      <c r="J38" s="9" t="n"/>
+      <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
@@ -1188,11 +1367,15 @@
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="8" t="n"/>
-      <c r="J39" s="9" t="n"/>
+      <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="6" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="8" t="n"/>
+      <c r="P39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
@@ -1202,11 +1385,15 @@
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="8" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
@@ -1216,11 +1403,15 @@
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="6" t="n"/>
       <c r="I41" s="8" t="n"/>
-      <c r="J41" s="9" t="n"/>
+      <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="8" t="n"/>
+      <c r="P41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
@@ -1230,11 +1421,15 @@
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="8" t="n"/>
-      <c r="J42" s="9" t="n"/>
+      <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="8" t="n"/>
+      <c r="P42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
@@ -1244,17 +1439,21 @@
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="8" t="n"/>
-      <c r="J43" s="9" t="n"/>
+      <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="6" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="8" t="n"/>
+      <c r="P43" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1268,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1284,100 +1483,112 @@
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>AIモデル</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>gemini-2.0-flash</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>評価対象</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>自己PR文（回答入力シートF列）</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>評価対象①</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>自己PR文（回答入力シートF列、書くこと）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>評価対象②</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>聞き取り評価①〜③（回答入力シートJ〜L列、聞くこと）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>知識・技能</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>3段階（A/B/C）</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>思考・判断・表現</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>5段階（S/A/B/C/D）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>思考・判断・表現（書くこと／聞くこと）</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>各5段階（S/A/B/C/D）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>データ範囲</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>回答入力シート 4行目〜43行目</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>ClassroomフォルダID</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>（ここにフォルダIDを入力）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>※ Gemini APIキーは、このシートには入力しません。GASの「プロジェクトの設定」→「スクリプト プロパティ」で GEMINI_API_KEY を設定してください。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="18" customHeight="1"/>
+    <row r="16" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:B16"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/materials/自己PR文を書く/教員用評価シート.xlsx
+++ b/materials/自己PR文を書く/教員用評価シート.xlsx
@@ -559,7 +559,7 @@
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="33.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>自己PR文を書く ―回答入力・評価シート―</t>
@@ -573,7 +573,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="78" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>クラス</t>
@@ -667,7 +667,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="254.8" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>3</t>
@@ -1474,7 +1474,7 @@
     <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="33.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI設定</t>
@@ -1482,7 +1482,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="28.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>AIモデル</t>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="28.7" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Temperature</t>
@@ -1504,7 +1504,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="5"/>
+    <row r="6" ht="28.7" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>評価対象①</t>
@@ -1516,7 +1517,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="47.4" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>評価対象②</t>
@@ -1528,7 +1529,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="28.7" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>知識・技能</t>
@@ -1540,7 +1541,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="66.09999999999999" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>思考・判断・表現（書くこと／聞くこと）</t>
@@ -1552,7 +1553,8 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="10"/>
+    <row r="11" ht="28.7" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>データ範囲</t>
@@ -1564,7 +1566,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="47.4" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>ClassroomフォルダID</t>
@@ -1576,15 +1578,16 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="13"/>
+    <row r="14" ht="19.48333333333333" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>※ Gemini APIキーは、このシートには入力しません。GASの「プロジェクトの設定」→「スクリプト プロパティ」で GEMINI_API_KEY を設定してください。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="18" customHeight="1"/>
+    <row r="15" ht="19.48333333333333" customHeight="1"/>
+    <row r="16" ht="19.48333333333333" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A14:B16"/>
